--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487401_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487401_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9576</v>
+        <v>4.0743</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9621</v>
+        <v>2.0411</v>
       </c>
       <c r="F2" t="n">
-        <v>2.9955</v>
+        <v>2.0332</v>
       </c>
       <c r="G2" t="n">
         <v>0.4084</v>
@@ -610,13 +610,13 @@
         <v>0.9792</v>
       </c>
       <c r="S2" t="n">
-        <v>3.4489</v>
+        <v>1.5656</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7993</v>
+        <v>-0.1218</v>
       </c>
       <c r="U2" t="n">
-        <v>2.6497</v>
+        <v>1.6874</v>
       </c>
       <c r="V2" t="n">
         <v>2.1003</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5779</v>
+        <v>4.0186</v>
       </c>
       <c r="E3" t="n">
-        <v>2.7039</v>
+        <v>3.0109</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8741</v>
+        <v>1.0077</v>
       </c>
       <c r="G3" t="n">
         <v>2.1976</v>
@@ -688,13 +688,13 @@
         <v>1.5668</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1278</v>
+        <v>-0.6871</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8316</v>
+        <v>-0.5246</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2961</v>
+        <v>-0.1625</v>
       </c>
       <c r="V3" t="n">
         <v>0.9412</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5578</v>
+        <v>2.2287</v>
       </c>
       <c r="E4" t="n">
-        <v>2.3384</v>
+        <v>1.929</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2195</v>
+        <v>0.2997</v>
       </c>
       <c r="G4" t="n">
         <v>1.6099</v>
@@ -766,13 +766,13 @@
         <v>1.9585</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3447</v>
+        <v>-0.6739000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1494</v>
+        <v>-0.5587</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1953</v>
+        <v>-0.1151</v>
       </c>
       <c r="V4" t="n">
         <v>-0.6659</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. QUIROS HERNANDEZ</t>
+          <t>D. CUETOS FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2811</v>
+        <v>1.3724</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6738</v>
+        <v>0.1867</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6073</v>
+        <v>1.1857</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6808</v>
+        <v>1.6249</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7241</v>
+        <v>0.8466</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.4049</v>
+        <v>0.7783</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.8235</v>
+        <v>2.0041</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0616</v>
+        <v>0.706</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.885</v>
+        <v>1.2981</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8573</v>
+        <v>-0.3792</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3375</v>
+        <v>0.1406</v>
       </c>
       <c r="O5" t="n">
         <v>-0.5198</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5668</v>
+        <v>0.3917</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5668</v>
+        <v>1.3709</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1544</v>
+        <v>-0.6442</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3276</v>
+        <v>-0.8381</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1732</v>
+        <v>0.1939</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5495</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8249</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>R. QUIROS HERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6833</v>
+        <v>1.1253</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.338</v>
+        <v>0.5715</v>
       </c>
       <c r="F6" t="n">
-        <v>3.0212</v>
+        <v>0.5538</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1083</v>
+        <v>-1.6808</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7554</v>
+        <v>0.7241</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.647</v>
+        <v>-2.4049</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.804</v>
+        <v>-0.8235</v>
       </c>
       <c r="K6" t="n">
-        <v>0.546</v>
+        <v>1.0616</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.35</v>
+        <v>-1.885</v>
       </c>
       <c r="M6" t="n">
-        <v>0.9124</v>
+        <v>-0.8573</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2094</v>
+        <v>-0.3375</v>
       </c>
       <c r="O6" t="n">
-        <v>0.703</v>
+        <v>-0.5198</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5875</v>
+        <v>1.5668</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3709</v>
+        <v>1.5668</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6048</v>
+        <v>-0.3102</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0098</v>
+        <v>-0.4299</v>
       </c>
       <c r="U6" t="n">
-        <v>0.405</v>
+        <v>0.1197</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7673</v>
+        <v>1.5495</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4344</v>
+        <v>1.8249</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3329</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. CUETOS FERNANDEZ</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6156</v>
+        <v>1.0437</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2226</v>
+        <v>-2.0309</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8381999999999999</v>
+        <v>3.0747</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6249</v>
+        <v>0.1083</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8466</v>
+        <v>0.7554</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7783</v>
+        <v>-0.647</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0041</v>
+        <v>-0.804</v>
       </c>
       <c r="K7" t="n">
-        <v>0.706</v>
+        <v>0.546</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2981</v>
+        <v>-1.35</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3792</v>
+        <v>0.9124</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1406</v>
+        <v>0.2094</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5198</v>
+        <v>0.703</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3917</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R7" t="n">
         <v>1.3709</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.401</v>
+        <v>-0.2444</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2474</v>
+        <v>-0.7028</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1536</v>
+        <v>0.4585</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.7673</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.4344</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3235</v>
+        <v>0.4663</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6374</v>
+        <v>0.4327</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3139</v>
+        <v>0.0336</v>
       </c>
       <c r="G8" t="n">
         <v>-0.1353</v>
@@ -1078,13 +1078,13 @@
         <v>1.5668</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4041</v>
+        <v>-0.2613</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.387</v>
+        <v>-0.5917</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0171</v>
+        <v>0.3304</v>
       </c>
       <c r="V8" t="n">
         <v>0.2754</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.3969</v>
+        <v>-0.2854</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7284</v>
+        <v>-1.8307</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3314</v>
+        <v>1.5453</v>
       </c>
       <c r="G9" t="n">
         <v>-3.5717</v>
@@ -1156,13 +1156,13 @@
         <v>1.3709</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.6987</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1494</v>
+        <v>-0.2517</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7366</v>
+        <v>0.9504</v>
       </c>
       <c r="V9" t="n">
         <v>1.2166</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4119</v>
+        <v>-1.2782</v>
       </c>
       <c r="E10" t="n">
         <v>-2.074</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6621</v>
+        <v>0.7958</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4206</v>
@@ -1234,13 +1234,13 @@
         <v>0.9792</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9913</v>
+        <v>-0.8576</v>
       </c>
       <c r="T10" t="n">
         <v>-0.5346</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4567</v>
+        <v>-0.323</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2755</v>
+        <v>-1.9555</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1567</v>
+        <v>-2.5427</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8812</v>
+        <v>0.5872000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>0.2613</v>
@@ -1312,13 +1312,13 @@
         <v>1.5668</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0128</v>
+        <v>0.3327</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.485</v>
+        <v>-0.871</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4978</v>
+        <v>1.2038</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1578</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.646</v>
+        <v>-2.5436</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6211</v>
+        <v>-1.5187</v>
       </c>
       <c r="F12" t="n">
         <v>-1.0249</v>
@@ -1390,10 +1390,10 @@
         <v>0.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.297</v>
+        <v>-0.1947</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.297</v>
+        <v>-0.1947</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.266500000000001</v>
+        <v>8.266599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.825199999999999</v>
+        <v>-1.8251</v>
       </c>
       <c r="F13" t="n">
-        <v>10.0917</v>
+        <v>10.0918</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3387</v>
@@ -1438,13 +1438,13 @@
         <v>1.7028</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.0414</v>
+        <v>-4.041399999999999</v>
       </c>
       <c r="J13" t="n">
         <v>2.4587</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6460000000000005</v>
+        <v>0.646</v>
       </c>
       <c r="L13" t="n">
         <v>1.813200000000001</v>
@@ -1468,13 +1468,13 @@
         <v>14.6885</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.276199999999999</v>
+        <v>-1.2764</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.6195</v>
+        <v>-5.619599999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>4.343500000000001</v>
+        <v>4.3435</v>
       </c>
       <c r="V13" t="n">
         <v>5.0266</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3901</v>
+        <v>6.5421</v>
       </c>
       <c r="E14" t="n">
-        <v>6.179</v>
+        <v>5.7697</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2111</v>
+        <v>0.7724</v>
       </c>
       <c r="G14" t="n">
         <v>3.7207</v>
@@ -1546,13 +1546,13 @@
         <v>0.9792</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2504</v>
+        <v>-0.0984</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2394</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.011</v>
+        <v>0.5504</v>
       </c>
       <c r="V14" t="n">
         <v>2.9198</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.2973</v>
+        <v>4.7405</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9815</v>
+        <v>2.8791</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3158</v>
+        <v>1.8614</v>
       </c>
       <c r="G15" t="n">
         <v>5.0227</v>
@@ -1624,13 +1624,13 @@
         <v>0.7834</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8673999999999999</v>
+        <v>0.3107</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.7863</v>
       </c>
       <c r="U15" t="n">
-        <v>1.5515</v>
+        <v>1.097</v>
       </c>
       <c r="V15" t="n">
         <v>-0.397</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.5894</v>
+        <v>1.9883</v>
       </c>
       <c r="E16" t="n">
-        <v>2.091</v>
+        <v>1.784</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4984</v>
+        <v>0.2043</v>
       </c>
       <c r="G16" t="n">
         <v>1.5444</v>
@@ -1702,13 +1702,13 @@
         <v>0.9792</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2408</v>
+        <v>0.6397</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3852</v>
+        <v>0.07820000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8556</v>
+        <v>0.5615</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9671</v>
+        <v>1.439</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.353</v>
+        <v>-0.1484</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3201</v>
+        <v>1.5874</v>
       </c>
       <c r="G17" t="n">
         <v>1.2994</v>
@@ -1780,13 +1780,13 @@
         <v>0.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.724</v>
+        <v>-0.252</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9504</v>
+        <v>-0.7458</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2264</v>
+        <v>0.4937</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. NIETO FONTAIÑA</t>
+          <t>A. ALVAREZ JORGE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,22 +1813,22 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3302</v>
+        <v>0.181</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1188</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.449</v>
+        <v>0.181</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2729</v>
+        <v>0.1364</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2729</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.1364</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1840,13 +1840,13 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2729</v>
+        <v>0.1364</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2729</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.1364</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1858,28 +1858,28 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3327</v>
+        <v>0.0446</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1188</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4515</v>
+        <v>0.0446</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. ALVAREZ JORGE</t>
+          <t>S. NIETO FONTAIÑA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,22 +1891,22 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1543</v>
+        <v>0.1163</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>-0.1188</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1543</v>
+        <v>0.2351</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1364</v>
+        <v>0.2729</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>0.2729</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1364</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1918,13 +1918,13 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1364</v>
+        <v>0.2729</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>0.2729</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1364</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
@@ -1936,22 +1936,22 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0178</v>
+        <v>0.1188</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-0.1188</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0178</v>
+        <v>0.2376</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3807</v>
+        <v>-1.2654</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.403</v>
+        <v>-1.9937</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0224</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>-0.782</v>
@@ -2014,13 +2014,13 @@
         <v>0.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4221</v>
+        <v>0.5374</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.594</v>
+        <v>-0.1847</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0161</v>
+        <v>0.7221</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2166</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3489</v>
+        <v>-1.9747</v>
       </c>
       <c r="E21" t="n">
         <v>-0.4922</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8567</v>
+        <v>-1.4825</v>
       </c>
       <c r="G21" t="n">
         <v>1.2008</v>
@@ -2092,13 +2092,13 @@
         <v>0.9792</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.428</v>
+        <v>-0.0538</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2682</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1599</v>
+        <v>0.2144</v>
       </c>
       <c r="V21" t="n">
         <v>-1.9466</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1129</v>
+        <v>-2.7257</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8209</v>
+        <v>-3.5139</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7079</v>
+        <v>0.7881</v>
       </c>
       <c r="G22" t="n">
         <v>-3.4216</v>
@@ -2170,13 +2170,13 @@
         <v>0.5875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2788</v>
+        <v>0.1084</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6534</v>
+        <v>-0.3464</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3746</v>
+        <v>0.4548</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.6422</v>
+        <v>-3.5039</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1505</v>
+        <v>-1.2529</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4916</v>
+        <v>-2.251</v>
       </c>
       <c r="G23" t="n">
         <v>0.1281</v>
@@ -2248,13 +2248,13 @@
         <v>0.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0351</v>
+        <v>0.1734</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1476</v>
+        <v>0.0453</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1125</v>
+        <v>0.1281</v>
       </c>
       <c r="V23" t="n">
         <v>-2.0427</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8007</v>
+        <v>-6.197</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.6618</v>
+        <v>-6.7641</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8611</v>
+        <v>0.5671</v>
       </c>
       <c r="G24" t="n">
         <v>-3.6277</v>
@@ -2326,13 +2326,13 @@
         <v>1.1751</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0063</v>
+        <v>-0.3901</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9216</v>
+        <v>-1.024</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9278999999999999</v>
+        <v>0.6339</v>
       </c>
       <c r="V24" t="n">
         <v>-1.3958</v>
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.7095</v>
+        <v>-7.6071</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.3429</v>
+        <v>-6.2406</v>
       </c>
       <c r="F25" t="n">
         <v>-1.3666</v>
@@ -2404,10 +2404,10 @@
         <v>1.1751</v>
       </c>
       <c r="S25" t="n">
-        <v>0.0353</v>
+        <v>0.1376</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4464</v>
+        <v>-0.3441</v>
       </c>
       <c r="U25" t="n">
         <v>0.4817</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-8.266500000000001</v>
+        <v>-8.266600000000002</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.0916</v>
+        <v>-10.0918</v>
       </c>
       <c r="F26" t="n">
-        <v>1.8252</v>
+        <v>1.825</v>
       </c>
       <c r="G26" t="n">
         <v>2.338700000000002</v>
@@ -2485,10 +2485,10 @@
         <v>1.2763</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.343399999999999</v>
+        <v>-4.3435</v>
       </c>
       <c r="U26" t="n">
-        <v>5.619700000000001</v>
+        <v>5.6198</v>
       </c>
       <c r="V26" t="n">
         <v>-5.026699999999999</v>
